--- a/artfynd/A 34638-2025 artfynd.xlsx
+++ b/artfynd/A 34638-2025 artfynd.xlsx
@@ -1403,7 +1403,7 @@
         <v>126694810</v>
       </c>
       <c r="B8" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>126694470</v>
       </c>
       <c r="B9" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1620,10 +1620,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126694528</v>
+        <v>126694682</v>
       </c>
       <c r="B10" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1663,14 +1663,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 34638, Sm</t>
+          <t>A 34368, Gölpefall, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581048</v>
+        <v>581053</v>
       </c>
       <c r="R10" t="n">
-        <v>6385199</v>
+        <v>6385210</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1730,10 +1730,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126694682</v>
+        <v>126694528</v>
       </c>
       <c r="B11" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1773,14 +1773,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 34368, Gölpefall, Sm</t>
+          <t>A 34638, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581053</v>
+        <v>581048</v>
       </c>
       <c r="R11" t="n">
-        <v>6385210</v>
+        <v>6385199</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1952,7 +1952,7 @@
         <v>126694584</v>
       </c>
       <c r="B13" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2059,10 +2059,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126694725</v>
+        <v>126694507</v>
       </c>
       <c r="B14" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581060</v>
+        <v>581074</v>
       </c>
       <c r="R14" t="n">
-        <v>6385201</v>
+        <v>6385192</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2169,10 +2169,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126694507</v>
+        <v>126694725</v>
       </c>
       <c r="B15" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581074</v>
+        <v>581060</v>
       </c>
       <c r="R15" t="n">
-        <v>6385192</v>
+        <v>6385201</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2282,7 +2282,7 @@
         <v>126694759</v>
       </c>
       <c r="B16" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>126694441</v>
       </c>
       <c r="B17" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>126694651</v>
       </c>
       <c r="B18" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2613,32 +2613,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126694965</v>
+        <v>126694703</v>
       </c>
       <c r="B19" t="n">
-        <v>57654</v>
+        <v>98436</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2646,13 +2646,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2660,13 +2664,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581001</v>
+        <v>581060</v>
       </c>
       <c r="R19" t="n">
-        <v>6385192</v>
+        <v>6385205</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2698,17 +2702,13 @@
           <t>2025-07-15</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På väg till sovplats. Varnade för mig.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2727,32 +2727,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126694703</v>
+        <v>126694965</v>
       </c>
       <c r="B20" t="n">
-        <v>98361</v>
+        <v>57654</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2760,17 +2760,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2778,13 +2774,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581060</v>
+        <v>581001</v>
       </c>
       <c r="R20" t="n">
-        <v>6385205</v>
+        <v>6385192</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2816,13 +2812,17 @@
           <t>2025-07-15</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På väg till sovplats. Varnade för mig.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2844,7 +2844,7 @@
         <v>126694632</v>
       </c>
       <c r="B21" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>126694419</v>
       </c>
       <c r="B22" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>126760034</v>
       </c>
       <c r="B24" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>126760048</v>
       </c>
       <c r="B25" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 34638-2025 artfynd.xlsx
+++ b/artfynd/A 34638-2025 artfynd.xlsx
@@ -1403,7 +1403,7 @@
         <v>126694810</v>
       </c>
       <c r="B8" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>126694470</v>
       </c>
       <c r="B9" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>126694682</v>
       </c>
       <c r="B10" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>126694528</v>
       </c>
       <c r="B11" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>126694584</v>
       </c>
       <c r="B13" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>126694507</v>
       </c>
       <c r="B14" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>126694725</v>
       </c>
       <c r="B15" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         <v>126694759</v>
       </c>
       <c r="B16" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>126694441</v>
       </c>
       <c r="B17" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>126694651</v>
       </c>
       <c r="B18" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2613,32 +2613,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126694703</v>
+        <v>126694965</v>
       </c>
       <c r="B19" t="n">
-        <v>98436</v>
+        <v>57654</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2646,17 +2646,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2664,13 +2660,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581060</v>
+        <v>581001</v>
       </c>
       <c r="R19" t="n">
-        <v>6385205</v>
+        <v>6385192</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2702,13 +2698,17 @@
           <t>2025-07-15</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På väg till sovplats. Varnade för mig.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2727,32 +2727,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126694965</v>
+        <v>126694703</v>
       </c>
       <c r="B20" t="n">
-        <v>57654</v>
+        <v>98442</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2760,13 +2760,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2774,13 +2778,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581001</v>
+        <v>581060</v>
       </c>
       <c r="R20" t="n">
-        <v>6385192</v>
+        <v>6385205</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2812,17 +2816,13 @@
           <t>2025-07-15</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På väg till sovplats. Varnade för mig.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2844,7 +2844,7 @@
         <v>126694632</v>
       </c>
       <c r="B21" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>126694419</v>
       </c>
       <c r="B22" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>126760034</v>
       </c>
       <c r="B24" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>126760048</v>
       </c>
       <c r="B25" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 34638-2025 artfynd.xlsx
+++ b/artfynd/A 34638-2025 artfynd.xlsx
@@ -1403,7 +1403,7 @@
         <v>126694810</v>
       </c>
       <c r="B8" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>126694470</v>
       </c>
       <c r="B9" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>126694682</v>
       </c>
       <c r="B10" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>126694528</v>
       </c>
       <c r="B11" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>126694584</v>
       </c>
       <c r="B13" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>126694507</v>
       </c>
       <c r="B14" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>126694725</v>
       </c>
       <c r="B15" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         <v>126694759</v>
       </c>
       <c r="B16" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>126694441</v>
       </c>
       <c r="B17" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>126694651</v>
       </c>
       <c r="B18" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2613,32 +2613,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126694965</v>
+        <v>126694703</v>
       </c>
       <c r="B19" t="n">
-        <v>57654</v>
+        <v>98443</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2646,13 +2646,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2660,13 +2664,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581001</v>
+        <v>581060</v>
       </c>
       <c r="R19" t="n">
-        <v>6385192</v>
+        <v>6385205</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2698,17 +2702,13 @@
           <t>2025-07-15</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På väg till sovplats. Varnade för mig.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2727,32 +2727,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126694703</v>
+        <v>126694965</v>
       </c>
       <c r="B20" t="n">
-        <v>98442</v>
+        <v>57654</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2760,17 +2760,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2778,13 +2774,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581060</v>
+        <v>581001</v>
       </c>
       <c r="R20" t="n">
-        <v>6385205</v>
+        <v>6385192</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2816,13 +2812,17 @@
           <t>2025-07-15</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På väg till sovplats. Varnade för mig.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2844,7 +2844,7 @@
         <v>126694632</v>
       </c>
       <c r="B21" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>126694419</v>
       </c>
       <c r="B22" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>126760034</v>
       </c>
       <c r="B24" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>126760048</v>
       </c>
       <c r="B25" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 34638-2025 artfynd.xlsx
+++ b/artfynd/A 34638-2025 artfynd.xlsx
@@ -2613,32 +2613,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126694703</v>
+        <v>126694965</v>
       </c>
       <c r="B19" t="n">
-        <v>98443</v>
+        <v>57654</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2646,17 +2646,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2664,13 +2660,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581060</v>
+        <v>581001</v>
       </c>
       <c r="R19" t="n">
-        <v>6385205</v>
+        <v>6385192</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2702,13 +2698,17 @@
           <t>2025-07-15</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På väg till sovplats. Varnade för mig.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2727,32 +2727,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126694965</v>
+        <v>126694703</v>
       </c>
       <c r="B20" t="n">
-        <v>57654</v>
+        <v>98443</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2760,13 +2760,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2774,13 +2778,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581001</v>
+        <v>581060</v>
       </c>
       <c r="R20" t="n">
-        <v>6385192</v>
+        <v>6385205</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2812,17 +2816,13 @@
           <t>2025-07-15</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På väg till sovplats. Varnade för mig.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 34638-2025 artfynd.xlsx
+++ b/artfynd/A 34638-2025 artfynd.xlsx
@@ -3064,7 +3064,7 @@
         <v>126760303</v>
       </c>
       <c r="B23" t="n">
-        <v>44801</v>
+        <v>44805</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>126760034</v>
       </c>
       <c r="B24" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>126760048</v>
       </c>
       <c r="B25" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>126760301</v>
       </c>
       <c r="B26" t="n">
-        <v>44806</v>
+        <v>44810</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 34638-2025 artfynd.xlsx
+++ b/artfynd/A 34638-2025 artfynd.xlsx
@@ -1403,7 +1403,7 @@
         <v>126694810</v>
       </c>
       <c r="B8" t="n">
-        <v>98443</v>
+        <v>98436</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>126694470</v>
       </c>
       <c r="B9" t="n">
-        <v>98443</v>
+        <v>98436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>126694682</v>
       </c>
       <c r="B10" t="n">
-        <v>98443</v>
+        <v>98436</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>126694528</v>
       </c>
       <c r="B11" t="n">
-        <v>98443</v>
+        <v>98436</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>126694584</v>
       </c>
       <c r="B13" t="n">
-        <v>98443</v>
+        <v>98436</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>126694507</v>
       </c>
       <c r="B14" t="n">
-        <v>98443</v>
+        <v>98436</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>126694725</v>
       </c>
       <c r="B15" t="n">
-        <v>98443</v>
+        <v>98436</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         <v>126694759</v>
       </c>
       <c r="B16" t="n">
-        <v>98443</v>
+        <v>98436</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>126694441</v>
       </c>
       <c r="B17" t="n">
-        <v>98443</v>
+        <v>98436</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>126694651</v>
       </c>
       <c r="B18" t="n">
-        <v>98443</v>
+        <v>98436</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2613,32 +2613,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126694965</v>
+        <v>126694703</v>
       </c>
       <c r="B19" t="n">
-        <v>57654</v>
+        <v>98436</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2646,13 +2646,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2660,13 +2664,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581001</v>
+        <v>581060</v>
       </c>
       <c r="R19" t="n">
-        <v>6385192</v>
+        <v>6385205</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2698,17 +2702,13 @@
           <t>2025-07-15</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På väg till sovplats. Varnade för mig.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2727,32 +2727,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126694703</v>
+        <v>126694965</v>
       </c>
       <c r="B20" t="n">
-        <v>98443</v>
+        <v>57654</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2760,17 +2760,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2778,13 +2774,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581060</v>
+        <v>581001</v>
       </c>
       <c r="R20" t="n">
-        <v>6385205</v>
+        <v>6385192</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2816,13 +2812,17 @@
           <t>2025-07-15</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På väg till sovplats. Varnade för mig.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2844,7 +2844,7 @@
         <v>126694632</v>
       </c>
       <c r="B21" t="n">
-        <v>98443</v>
+        <v>98436</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>126694419</v>
       </c>
       <c r="B22" t="n">
-        <v>98443</v>
+        <v>98436</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>126760303</v>
       </c>
       <c r="B23" t="n">
-        <v>44805</v>
+        <v>44801</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>126760034</v>
       </c>
       <c r="B24" t="n">
-        <v>98447</v>
+        <v>98436</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>126760048</v>
       </c>
       <c r="B25" t="n">
-        <v>98447</v>
+        <v>98436</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>126760301</v>
       </c>
       <c r="B26" t="n">
-        <v>44810</v>
+        <v>44806</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 34638-2025 artfynd.xlsx
+++ b/artfynd/A 34638-2025 artfynd.xlsx
@@ -1403,7 +1403,7 @@
         <v>126694810</v>
       </c>
       <c r="B8" t="n">
-        <v>98436</v>
+        <v>98443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>126694470</v>
       </c>
       <c r="B9" t="n">
-        <v>98436</v>
+        <v>98443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>126694682</v>
       </c>
       <c r="B10" t="n">
-        <v>98436</v>
+        <v>98443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>126694528</v>
       </c>
       <c r="B11" t="n">
-        <v>98436</v>
+        <v>98443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>126694584</v>
       </c>
       <c r="B13" t="n">
-        <v>98436</v>
+        <v>98443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>126694507</v>
       </c>
       <c r="B14" t="n">
-        <v>98436</v>
+        <v>98443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>126694725</v>
       </c>
       <c r="B15" t="n">
-        <v>98436</v>
+        <v>98443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         <v>126694759</v>
       </c>
       <c r="B16" t="n">
-        <v>98436</v>
+        <v>98443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>126694441</v>
       </c>
       <c r="B17" t="n">
-        <v>98436</v>
+        <v>98443</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>126694651</v>
       </c>
       <c r="B18" t="n">
-        <v>98436</v>
+        <v>98443</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2613,32 +2613,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126694703</v>
+        <v>126694965</v>
       </c>
       <c r="B19" t="n">
-        <v>98436</v>
+        <v>57654</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2646,17 +2646,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2664,13 +2660,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581060</v>
+        <v>581001</v>
       </c>
       <c r="R19" t="n">
-        <v>6385205</v>
+        <v>6385192</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2702,13 +2698,17 @@
           <t>2025-07-15</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På väg till sovplats. Varnade för mig.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2727,32 +2727,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126694965</v>
+        <v>126694703</v>
       </c>
       <c r="B20" t="n">
-        <v>57654</v>
+        <v>98443</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2760,13 +2760,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2774,13 +2778,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581001</v>
+        <v>581060</v>
       </c>
       <c r="R20" t="n">
-        <v>6385192</v>
+        <v>6385205</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2812,17 +2816,13 @@
           <t>2025-07-15</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På väg till sovplats. Varnade för mig.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2844,7 +2844,7 @@
         <v>126694632</v>
       </c>
       <c r="B21" t="n">
-        <v>98436</v>
+        <v>98443</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>126694419</v>
       </c>
       <c r="B22" t="n">
-        <v>98436</v>
+        <v>98443</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>126760303</v>
       </c>
       <c r="B23" t="n">
-        <v>44801</v>
+        <v>44805</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>126760034</v>
       </c>
       <c r="B24" t="n">
-        <v>98436</v>
+        <v>98447</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>126760048</v>
       </c>
       <c r="B25" t="n">
-        <v>98436</v>
+        <v>98447</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>126760301</v>
       </c>
       <c r="B26" t="n">
-        <v>44806</v>
+        <v>44810</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 34638-2025 artfynd.xlsx
+++ b/artfynd/A 34638-2025 artfynd.xlsx
@@ -2616,7 +2616,7 @@
         <v>126694965</v>
       </c>
       <c r="B19" t="n">
-        <v>57881</v>
+        <v>57654</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
